--- a/aircraft/reports/manufacturer/McDonnel-Douglas/aircraft-type-pie-chart.xlsx
+++ b/aircraft/reports/manufacturer/McDonnel-Douglas/aircraft-type-pie-chart.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6533,6 +6533,67 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>15560</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>45906</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Abingdon</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Western Global Airlines</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>KD8187</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>OST</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>NGU</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>N543JN</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>48543</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>MD-11F</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>McDonnel Douglas</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
